--- a/Team-Data/2007-08/4-15-2007-08.xlsx
+++ b/Team-Data/2007-08/4-15-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
         <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>0.457</v>
+        <v>0.463</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J2" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.454</v>
@@ -688,7 +755,7 @@
         <v>4.7</v>
       </c>
       <c r="M2" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="N2" t="n">
         <v>0.357</v>
@@ -697,7 +764,7 @@
         <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0.773</v>
@@ -724,22 +791,22 @@
         <v>5.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z2" t="n">
         <v>20.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -751,7 +818,7 @@
         <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI2" t="n">
         <v>22</v>
@@ -769,13 +836,13 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -802,7 +869,7 @@
         <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -984,10 +1051,10 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
         <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>0.383</v>
+        <v>0.388</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I4" t="n">
         <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -1058,22 +1125,22 @@
         <v>0.367</v>
       </c>
       <c r="O4" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P4" t="n">
         <v>25.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.713</v>
+        <v>0.711</v>
       </c>
       <c r="R4" t="n">
         <v>10.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U4" t="n">
         <v>21.2</v>
@@ -1085,7 +1152,7 @@
         <v>7.5</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
         <v>5.9</v>
@@ -1094,34 +1161,34 @@
         <v>21.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC4" t="n">
         <v>-4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>18</v>
@@ -1136,7 +1203,7 @@
         <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1154,7 +1221,7 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
@@ -1175,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1318,7 +1385,7 @@
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
         <v>18</v>
@@ -1339,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1873,7 +1940,7 @@
         <v>19</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>0.716</v>
+        <v>0.713</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1956,40 +2023,40 @@
         <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S9" t="n">
         <v>29.5</v>
       </c>
       <c r="T9" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U9" t="n">
         <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
@@ -2007,13 +2074,13 @@
         <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,16 +2095,16 @@
         <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>22</v>
@@ -2046,7 +2113,7 @@
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
         <v>22</v>
@@ -2055,7 +2122,7 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
         <v>25</v>
@@ -2064,7 +2131,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2088,7 +2155,7 @@
         <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
@@ -2207,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
@@ -2246,7 +2313,7 @@
         <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
@@ -2389,16 +2456,16 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>10</v>
@@ -2449,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2580,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,7 +2748,7 @@
         <v>34.5</v>
       </c>
       <c r="J13" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K13" t="n">
         <v>0.438</v>
@@ -2693,19 +2760,19 @@
         <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P13" t="n">
         <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S13" t="n">
         <v>30.3</v>
@@ -2729,19 +2796,19 @@
         <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.1</v>
+        <v>-7</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,13 +2820,13 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2789,7 +2856,7 @@
         <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU13" t="n">
         <v>16</v>
@@ -2807,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.695</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2878,16 +2945,16 @@
         <v>0.378</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S14" t="n">
         <v>33.2</v>
@@ -2896,13 +2963,13 @@
         <v>44.1</v>
       </c>
       <c r="U14" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V14" t="n">
         <v>14.1</v>
       </c>
       <c r="W14" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X14" t="n">
         <v>5.3</v>
@@ -2911,16 +2978,16 @@
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.6</v>
+        <v>108.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2953,7 +3020,7 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" t="n">
         <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0.272</v>
+        <v>0.275</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
         <v>81.90000000000001</v>
@@ -3054,28 +3121,28 @@
         <v>7.5</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O15" t="n">
         <v>18.6</v>
       </c>
       <c r="P15" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.723</v>
+        <v>0.725</v>
       </c>
       <c r="R15" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S15" t="n">
         <v>31.2</v>
       </c>
       <c r="T15" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U15" t="n">
         <v>19</v>
@@ -3096,28 +3163,28 @@
         <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
@@ -3135,16 +3202,16 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,7 +3220,7 @@
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3490,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -3517,19 +3584,19 @@
         <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="n">
         <v>21</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>0.259</v>
+        <v>0.263</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J18" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
@@ -3603,28 +3670,28 @@
         <v>15.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O18" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.736</v>
+        <v>0.738</v>
       </c>
       <c r="R18" t="n">
         <v>11.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
         <v>14.6</v>
@@ -3645,13 +3712,13 @@
         <v>17.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3681,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3699,13 +3766,13 @@
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
@@ -3714,7 +3781,7 @@
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" t="n">
         <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.42</v>
+        <v>0.413</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I19" t="n">
         <v>34.9</v>
       </c>
       <c r="J19" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.443</v>
@@ -3782,31 +3849,31 @@
         <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N19" t="n">
         <v>0.347</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P19" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.735</v>
       </c>
       <c r="R19" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S19" t="n">
         <v>30.7</v>
       </c>
       <c r="T19" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>15</v>
@@ -3821,19 +3888,19 @@
         <v>4.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3845,16 +3912,16 @@
         <v>21</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
       </c>
       <c r="AJ19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK19" t="n">
         <v>25</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>18</v>
@@ -3869,13 +3936,13 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
         <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
         <v>13</v>
@@ -3890,7 +3957,7 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
         <v>16</v>
@@ -3899,7 +3966,7 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -3937,46 +4004,46 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J20" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L20" t="n">
         <v>7.7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P20" t="n">
         <v>20.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R20" t="n">
         <v>11.4</v>
@@ -3985,13 +4052,13 @@
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W20" t="n">
         <v>7.8</v>
@@ -4006,16 +4073,16 @@
         <v>18.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4027,7 +4094,7 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>-6.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
         <v>3</v>
@@ -4221,7 +4288,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
@@ -4236,13 +4303,13 @@
         <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR21" t="n">
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4254,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -4301,43 +4368,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="H22" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J22" t="n">
         <v>78.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O22" t="n">
         <v>20.3</v>
       </c>
       <c r="P22" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.722</v>
@@ -4352,7 +4419,7 @@
         <v>42</v>
       </c>
       <c r="U22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V22" t="n">
         <v>14.4</v>
@@ -4364,22 +4431,22 @@
         <v>4.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
         <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4394,10 +4461,10 @@
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4436,7 +4503,7 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>0.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4576,7 +4643,7 @@
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
@@ -4615,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>6</v>
@@ -4755,7 +4822,7 @@
         <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4809,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
         <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J25" t="n">
         <v>79.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M25" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O25" t="n">
         <v>17.3</v>
@@ -4886,19 +4953,19 @@
         <v>22.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R25" t="n">
         <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T25" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U25" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
         <v>13</v>
@@ -4913,40 +4980,40 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,7 +5022,7 @@
         <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>24</v>
@@ -4964,19 +5031,19 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>25</v>
       </c>
       <c r="AU25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
@@ -4985,19 +5052,19 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
         <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
         <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>0.463</v>
+        <v>0.469</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,7 +5114,7 @@
         <v>37.1</v>
       </c>
       <c r="J26" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.464</v>
@@ -5059,31 +5126,31 @@
         <v>16.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="P26" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="R26" t="n">
         <v>10.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T26" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U26" t="n">
         <v>19.1</v>
       </c>
       <c r="V26" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W26" t="n">
         <v>7.9</v>
@@ -5101,10 +5168,10 @@
         <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
@@ -5137,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5152,7 +5219,7 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5161,7 +5228,7 @@
         <v>28</v>
       </c>
       <c r="AV26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW26" t="n">
         <v>7</v>
@@ -5176,7 +5243,7 @@
         <v>24</v>
       </c>
       <c r="BA26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>5</v>
@@ -5301,13 +5368,13 @@
         <v>5</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>27</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>28</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
@@ -5337,7 +5404,7 @@
         <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU27" t="n">
         <v>21</v>
@@ -5346,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5513,7 +5580,7 @@
         <v>9</v>
       </c>
       <c r="AR28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>4</v>
@@ -5522,7 +5589,7 @@
         <v>3</v>
       </c>
       <c r="AU28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
@@ -5701,13 +5768,13 @@
         <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>7.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>6</v>
@@ -5847,7 +5914,7 @@
         <v>6</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
         <v>4</v>
@@ -5904,13 +5971,13 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6029,7 +6096,7 @@
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="n">
         <v>19</v>
@@ -6047,7 +6114,7 @@
         <v>9</v>
       </c>
       <c r="AN31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-15-2007-08</t>
+          <t>2008-04-15</t>
         </is>
       </c>
     </row>
